--- a/outputs/54474.xlsx
+++ b/outputs/54474.xlsx
@@ -249,68 +249,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -633,82 +637,82 @@
   <dimension ref="C3:H8"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.66"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <f aca="false">VLOOKUP(C7,'WHP DATA'!$B$4:$E$39,2,FALSE())</f>
+      <c r="E7" s="7" t="n">
+        <f aca="false">VLOOKUP($C7,'WHP DATA'!$B$4:$E$40,2,FALSE())</f>
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <f aca="false">VLOOKUP(C7,'WHP DATA'!$B$4:$E$39,3,FALSE())</f>
+      <c r="F7" s="7" t="n">
+        <f aca="false">VLOOKUP($C7,'WHP DATA'!$B$4:$E$40,3,FALSE())</f>
         <v>18</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <f aca="false">VLOOKUP(C7,'WHP DATA'!$B$4:$E$39,4,FALSE())</f>
+      <c r="G7" s="7" t="n">
+        <f aca="false">VLOOKUP($C7,'WHP DATA'!$B$4:$E$40,4,FALSE())</f>
         <v>0</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="8" t="n">
         <f aca="false">SUM(E7:G7)</f>
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <f aca="false">VLOOKUP(C8,'WHP DATA'!$B$4:$E$39,2,FALSE())</f>
+      <c r="E8" s="10" t="n">
+        <f aca="false">VLOOKUP($C8,'WHP DATA'!$B$4:$E$40,2,FALSE())</f>
         <v>1</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <f aca="false">VLOOKUP(C8,'WHP DATA'!$B$4:$E$39,3,FALSE())</f>
+      <c r="F8" s="10" t="n">
+        <f aca="false">VLOOKUP($C8,'WHP DATA'!$B$4:$E$40,3,FALSE())</f>
         <v>3</v>
       </c>
-      <c r="G8" s="9" t="n">
-        <f aca="false">VLOOKUP(C8,'WHP DATA'!$B$4:$E$39,4,FALSE())</f>
+      <c r="G8" s="10" t="n">
+        <f aca="false">VLOOKUP($C8,'WHP DATA'!$B$4:$E$40,4,FALSE())</f>
         <v>2</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="8" t="n">
         <f aca="false">SUM(E8:G8)</f>
         <v>6</v>
       </c>
@@ -735,318 +739,318 @@
   <dimension ref="B1:E41"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="41.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="12"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <f aca="false">SUM(C4:C17)</f>
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <f aca="false">SUM(D4:D17)</f>
         <v>18</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <f aca="false">SUM(E4:E17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="14"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="15" t="n">
+      <c r="C40" s="16" t="n">
         <f aca="false">SUM(C22:C39)</f>
         <v>1</v>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="16" t="n">
         <f aca="false">SUM(D22:D39)</f>
         <v>3</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E40" s="16" t="n">
         <f aca="false">SUM(E22:E39)</f>
         <v>2</v>
       </c>
